--- a/trade/fund_value_graphy.xlsx
+++ b/trade/fund_value_graphy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHUIQ\OneDrive\python项目\TuShare\trade\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73cc4880b9aaa2e9/python项目/MyFunds/MyFunds/trade/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BAAFF4-AE9C-4666-A0D5-3F3214BF27A4}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{F9BAAFF4-AE9C-4666-A0D5-3F3214BF27A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{49BAEF53-C9F7-4968-AB11-00A583D0C0AD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11508" windowHeight="8448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fund_value" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
